--- a/diseases/d145/1990-1994.xlsx
+++ b/diseases/d145/1990-1994.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5086,9 +5053,6 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
